--- a/public/plantilla-com-orden.xlsx
+++ b/public/plantilla-com-orden.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="hh:mm"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot; #,##0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot; #,##0"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -197,7 +197,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -295,6 +295,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6FAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -600,7 +605,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
@@ -725,34 +730,34 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -938,7 +943,7 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -947,7 +952,7 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -968,28 +973,28 @@
     <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1102,11 +1107,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1121,9 +1126,34 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11414,43 +11444,43 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>862393</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>862393</colOff>
+      <row>5</row>
+      <rowOff>131445</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11752,13 +11782,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="4" tint="0.3999755851924192"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.77734375" customWidth="1" style="67" min="1" max="1"/>
-    <col width="13" customWidth="1" style="67" min="2" max="3"/>
+    <col width="13" customWidth="1" style="67" min="2" max="2"/>
     <col width="13" customWidth="1" style="67" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="67" min="4" max="4"/>
     <col width="10" customWidth="1" style="67" min="5" max="5"/>
@@ -11816,7 +11847,7 @@
         </is>
       </c>
       <c r="I5" s="29" t="n"/>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" s="190" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
@@ -11835,7 +11866,7 @@
         </is>
       </c>
       <c r="I6" s="29" t="n"/>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" s="190" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
@@ -11854,7 +11885,7 @@
       <c r="G7" s="68" t="n"/>
       <c r="H7" s="68" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" s="190" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
@@ -11873,7 +11904,7 @@
       <c r="G8" s="68" t="n"/>
       <c r="H8" s="68" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="190" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
@@ -11886,7 +11917,7 @@
       <c r="L8" s="32" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="67">
-      <c r="A9" s="121" t="inlineStr">
+      <c r="A9" s="191" t="inlineStr">
         <is>
           <t>Cada orden queda ligada a un capítulo del presupuesto para saber cuánto se ha comprometido</t>
         </is>
@@ -11922,7 +11953,7 @@
       <c r="L10" s="17" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1" s="67">
-      <c r="A11" s="122" t="inlineStr">
+      <c r="A11" s="192" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
@@ -11933,7 +11964,7 @@
       <c r="E11" s="162" t="n"/>
       <c r="F11" s="162" t="n"/>
       <c r="G11" s="163" t="n"/>
-      <c r="H11" s="122" t="inlineStr">
+      <c r="H11" s="192" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
@@ -11944,7 +11975,7 @@
       <c r="L11" s="163" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="67">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="192" t="inlineStr">
         <is>
           <t>Fecha de la orden</t>
         </is>
@@ -11955,7 +11986,7 @@
       <c r="E12" s="162" t="n"/>
       <c r="F12" s="162" t="n"/>
       <c r="G12" s="163" t="n"/>
-      <c r="H12" s="122" t="inlineStr">
+      <c r="H12" s="192" t="inlineStr">
         <is>
           <t>Orden de compra N°</t>
         </is>
@@ -11966,7 +11997,7 @@
       <c r="L12" s="163" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="67">
-      <c r="A13" s="122" t="inlineStr">
+      <c r="A13" s="192" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
@@ -11977,7 +12008,7 @@
       <c r="E13" s="162" t="n"/>
       <c r="F13" s="162" t="n"/>
       <c r="G13" s="163" t="n"/>
-      <c r="H13" s="122" t="inlineStr">
+      <c r="H13" s="192" t="inlineStr">
         <is>
           <t>NIT</t>
         </is>
@@ -11988,7 +12019,7 @@
       <c r="L13" s="163" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="67">
-      <c r="A14" s="122" t="inlineStr">
+      <c r="A14" s="192" t="inlineStr">
         <is>
           <t>Requisición N°</t>
         </is>
@@ -11999,7 +12030,7 @@
       <c r="E14" s="162" t="n"/>
       <c r="F14" s="162" t="n"/>
       <c r="G14" s="163" t="n"/>
-      <c r="H14" s="122" t="inlineStr">
+      <c r="H14" s="192" t="inlineStr">
         <is>
           <t>Cuadro comparativo N°</t>
         </is>
@@ -12010,7 +12041,7 @@
       <c r="L14" s="163" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="67">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="192" t="inlineStr">
         <is>
           <t>Capítulo del presupuesto</t>
         </is>
@@ -12021,7 +12052,7 @@
       <c r="E15" s="162" t="n"/>
       <c r="F15" s="162" t="n"/>
       <c r="G15" s="163" t="n"/>
-      <c r="H15" s="122" t="inlineStr">
+      <c r="H15" s="192" t="inlineStr">
         <is>
           <t>Tipo de costo</t>
         </is>
@@ -12050,12 +12081,12 @@
       <c r="L16" s="17" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1" s="67">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="193" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B17" s="124" t="inlineStr">
+      <c r="B17" s="194" t="inlineStr">
         <is>
           <t>Descripción del material o servicio</t>
         </is>
@@ -12064,23 +12095,23 @@
       <c r="D17" s="31" t="n"/>
       <c r="E17" s="31" t="n"/>
       <c r="F17" s="32" t="n"/>
-      <c r="G17" s="124" t="inlineStr">
+      <c r="G17" s="194" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="H17" s="124" t="inlineStr">
+      <c r="H17" s="194" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="I17" s="124" t="inlineStr">
+      <c r="I17" s="194" t="inlineStr">
         <is>
           <t>Precio unitario</t>
         </is>
       </c>
       <c r="J17" s="32" t="n"/>
-      <c r="K17" s="124" t="inlineStr">
+      <c r="K17" s="194" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
@@ -12346,18 +12377,18 @@
       <c r="L33" s="17" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1" s="67">
-      <c r="A34" s="122" t="inlineStr">
+      <c r="A34" s="192" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
       <c r="B34" s="32" t="n"/>
-      <c r="C34" s="189" t="n"/>
+      <c r="C34" s="195" t="n"/>
       <c r="D34" s="162" t="n"/>
       <c r="E34" s="162" t="n"/>
       <c r="F34" s="162" t="n"/>
       <c r="G34" s="163" t="n"/>
-      <c r="H34" s="122" t="inlineStr">
+      <c r="H34" s="192" t="inlineStr">
         <is>
           <t>IVA (%)</t>
         </is>
@@ -12368,24 +12399,24 @@
       <c r="L34" s="163" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1" s="67">
-      <c r="A35" s="122" t="inlineStr">
+      <c r="A35" s="192" t="inlineStr">
         <is>
           <t>Valor del IVA</t>
         </is>
       </c>
       <c r="B35" s="32" t="n"/>
-      <c r="C35" s="189" t="n"/>
+      <c r="C35" s="195" t="n"/>
       <c r="D35" s="162" t="n"/>
       <c r="E35" s="162" t="n"/>
       <c r="F35" s="162" t="n"/>
       <c r="G35" s="163" t="n"/>
-      <c r="H35" s="122" t="inlineStr">
+      <c r="H35" s="192" t="inlineStr">
         <is>
           <t>Valor total de la orden</t>
         </is>
       </c>
       <c r="I35" s="32" t="n"/>
-      <c r="J35" s="189" t="n"/>
+      <c r="J35" s="195" t="n"/>
       <c r="K35" s="162" t="n"/>
       <c r="L35" s="163" t="n"/>
     </row>
@@ -12408,7 +12439,7 @@
       <c r="L36" s="17" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1" s="67">
-      <c r="A37" s="122" t="inlineStr">
+      <c r="A37" s="192" t="inlineStr">
         <is>
           <t>Lugar de entrega</t>
         </is>
@@ -12419,7 +12450,7 @@
       <c r="E37" s="162" t="n"/>
       <c r="F37" s="162" t="n"/>
       <c r="G37" s="163" t="n"/>
-      <c r="H37" s="122" t="inlineStr">
+      <c r="H37" s="192" t="inlineStr">
         <is>
           <t>Fecha de entrega prometida</t>
         </is>
@@ -12430,7 +12461,7 @@
       <c r="L37" s="163" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1" s="67">
-      <c r="A38" s="122" t="inlineStr">
+      <c r="A38" s="192" t="inlineStr">
         <is>
           <t>Forma de pago</t>
         </is>
@@ -12441,7 +12472,7 @@
       <c r="E38" s="162" t="n"/>
       <c r="F38" s="162" t="n"/>
       <c r="G38" s="163" t="n"/>
-      <c r="H38" s="122" t="inlineStr">
+      <c r="H38" s="192" t="inlineStr">
         <is>
           <t>Estado de la orden</t>
         </is>
@@ -12452,7 +12483,7 @@
       <c r="L38" s="163" t="n"/>
     </row>
     <row r="39" ht="45" customHeight="1" s="67">
-      <c r="A39" s="122" t="inlineStr">
+      <c r="A39" s="192" t="inlineStr">
         <is>
           <t>Condiciones y observaciones</t>
         </is>
@@ -12488,7 +12519,7 @@
       <c r="L40" s="17" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="67">
-      <c r="A41" s="130" t="inlineStr">
+      <c r="A41" s="196" t="inlineStr">
         <is>
           <t>ELABORA — COMPRAS</t>
         </is>
@@ -12496,7 +12527,7 @@
       <c r="B41" s="31" t="n"/>
       <c r="C41" s="31" t="n"/>
       <c r="D41" s="32" t="n"/>
-      <c r="E41" s="130" t="inlineStr">
+      <c r="E41" s="196" t="inlineStr">
         <is>
           <t>APRUEBA — DIRECTOR DE OBRA / GERENCIA</t>
         </is>
@@ -12504,7 +12535,7 @@
       <c r="F41" s="31" t="n"/>
       <c r="G41" s="31" t="n"/>
       <c r="H41" s="32" t="n"/>
-      <c r="I41" s="130" t="inlineStr">
+      <c r="I41" s="196" t="inlineStr">
         <is>
           <t>ACEPTA — PROVEEDOR</t>
         </is>
@@ -12514,7 +12545,7 @@
       <c r="L41" s="32" t="n"/>
     </row>
     <row r="42" ht="42" customHeight="1" s="67">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="197" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12522,7 +12553,7 @@
       <c r="B42" s="17" t="n"/>
       <c r="C42" s="170" t="n"/>
       <c r="D42" s="172" t="n"/>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E42" s="197" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12530,7 +12561,7 @@
       <c r="F42" s="17" t="n"/>
       <c r="G42" s="170" t="n"/>
       <c r="H42" s="172" t="n"/>
-      <c r="I42" s="18" t="inlineStr">
+      <c r="I42" s="197" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12540,7 +12571,7 @@
       <c r="L42" s="172" t="n"/>
     </row>
     <row r="43" ht="21" customHeight="1" s="67">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="197" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12548,7 +12579,7 @@
       <c r="B43" s="17" t="n"/>
       <c r="C43" s="170" t="n"/>
       <c r="D43" s="172" t="n"/>
-      <c r="E43" s="18" t="inlineStr">
+      <c r="E43" s="197" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12556,7 +12587,7 @@
       <c r="F43" s="17" t="n"/>
       <c r="G43" s="170" t="n"/>
       <c r="H43" s="172" t="n"/>
-      <c r="I43" s="18" t="inlineStr">
+      <c r="I43" s="197" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12566,7 +12597,7 @@
       <c r="L43" s="172" t="n"/>
     </row>
     <row r="44" ht="21" customHeight="1" s="67">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="197" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12574,7 +12605,7 @@
       <c r="B44" s="17" t="n"/>
       <c r="C44" s="170" t="n"/>
       <c r="D44" s="172" t="n"/>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E44" s="197" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12582,7 +12613,7 @@
       <c r="F44" s="17" t="n"/>
       <c r="G44" s="170" t="n"/>
       <c r="H44" s="172" t="n"/>
-      <c r="I44" s="18" t="inlineStr">
+      <c r="I44" s="197" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12663,8 +12694,8 @@
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="D6:I6"/>
     <mergeCell ref="A39:B39"/>
+    <mergeCell ref="J15:L15"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="J15:L15"/>
     <mergeCell ref="K30:L30"/>
     <mergeCell ref="C34:G34"/>
     <mergeCell ref="C39:L39"/>
